--- a/app/src/main/assets/methodmesh/odk_templates/svgselector/example_odk_svg_select.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/svgselector/example_odk_svg_select.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R8a1b3934f2d54119"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R559dc684c5e54543"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Ra2822c3015654bd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rd3d3f9095fda49a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rd1ad800159fe438c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rc1dc260dd09b4225"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -315,8 +315,8 @@
       <x:c r="E2" s="4" t="str">
         <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='svg.select',input_svg_name='bodymap_black.svg',input_selection_mode='sequence',return_mode='flat')</x:v>
       </x:c>
-      <x:c r="F2" s="4" t="str"/>
-      <x:c r="G2" s="4" t="str"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="4" t="str">
@@ -328,12 +328,12 @@
       <x:c r="C3" s="4" t="str">
         <x:v>SVG filename</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="str"/>
-      <x:c r="E3" s="4" t="str"/>
+      <x:c r="D3" s="4"/>
+      <x:c r="E3" s="4"/>
       <x:c r="F3" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G3" s="4" t="str"/>
+      <x:c r="G3" s="4"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="4" t="str">
@@ -345,12 +345,12 @@
       <x:c r="C4" s="4" t="str">
         <x:v>Selection mode</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="str"/>
-      <x:c r="E4" s="4" t="str"/>
+      <x:c r="D4" s="4"/>
+      <x:c r="E4" s="4"/>
       <x:c r="F4" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G4" s="4" t="str"/>
+      <x:c r="G4" s="4"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="4" t="str">
@@ -362,91 +362,176 @@
       <x:c r="C5" s="4" t="str">
         <x:v>Selected polygons</x:v>
       </x:c>
-      <x:c r="D5" s="4" t="str"/>
-      <x:c r="E5" s="4" t="str"/>
+      <x:c r="D5" s="4"/>
+      <x:c r="E5" s="4"/>
       <x:c r="F5" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G5" s="4" t="str"/>
+      <x:c r="G5" s="4"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="4" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>selection_events</x:v>
+        <x:v>selected_polygon_ids</x:v>
       </x:c>
       <x:c r="C6" s="4" t="str">
-        <x:v>Selection events</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="str"/>
-      <x:c r="E6" s="4" t="str"/>
+        <x:v>Selected polygon IDs</x:v>
+      </x:c>
+      <x:c r="D6" s="4"/>
+      <x:c r="E6" s="4"/>
       <x:c r="F6" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G6" s="4" t="str"/>
+      <x:c r="G6" s="4"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="4" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>selection_audit_hash</x:v>
+        <x:v>selected_count</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
-        <x:v>Selection audit hash</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="str"/>
-      <x:c r="E7" s="4" t="str"/>
+        <x:v>Selected polygon count</x:v>
+      </x:c>
+      <x:c r="D7" s="4"/>
+      <x:c r="E7" s="4"/>
       <x:c r="F7" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G7" s="4" t="str"/>
+      <x:c r="G7" s="4"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="4" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>selection_started_at</x:v>
+        <x:v>selection_summary</x:v>
       </x:c>
       <x:c r="C8" s="4" t="str">
-        <x:v>Selection started</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="str"/>
-      <x:c r="E8" s="4" t="str"/>
+        <x:v>Selection summary</x:v>
+      </x:c>
+      <x:c r="D8" s="4"/>
+      <x:c r="E8" s="4"/>
       <x:c r="F8" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G8" s="4" t="str"/>
+      <x:c r="G8" s="4"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="4" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>selection_completed_at</x:v>
+        <x:v>polygon_levels</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
-        <x:v>Selection completed</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="str"/>
-      <x:c r="E9" s="4" t="str"/>
+        <x:v>Polygon heat levels</x:v>
+      </x:c>
+      <x:c r="D9" s="4"/>
+      <x:c r="E9" s="4"/>
       <x:c r="F9" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G9" s="4" t="str"/>
+      <x:c r="G9" s="4"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="4" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="str">
+        <x:v>heatmap_max_level</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="str">
+        <x:v>Heat-map maximum level</x:v>
+      </x:c>
+      <x:c r="D10" s="4"/>
+      <x:c r="E10" s="4"/>
+      <x:c r="F10" s="4" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G10" s="4"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>selection_events</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Selection events</x:v>
+      </x:c>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>selection_audit_hash</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Selection audit hash</x:v>
+      </x:c>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>selection_started_at</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Selection started</x:v>
+      </x:c>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>selection_completed_at</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Selection completed</x:v>
+      </x:c>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="G14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
         <x:v>end_group</x:v>
       </x:c>
-      <x:c r="B10" s="4" t="str"/>
-      <x:c r="C10" s="4" t="str"/>
-      <x:c r="D10" s="4" t="str"/>
-      <x:c r="E10" s="4" t="str"/>
-      <x:c r="F10" s="4" t="str"/>
-      <x:c r="G10" s="4" t="str"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -506,6 +591,17 @@
         <x:v>Select in sequence</x:v>
       </x:c>
     </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>selection_mode</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>heatmap</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Heat map / repeated taps</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -539,7 +635,7 @@
         <x:v>svg_select</x:v>
       </x:c>
       <x:c r="C2" s="4" t="str">
-        <x:v>2026090703</x:v>
+        <x:v>2026091302</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
